--- a/backend/yudao-module-eam/src/main/resources/eam/eam-category-config-template.xlsx
+++ b/backend/yudao-module-eam/src/main/resources/eam/eam-category-config-template.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类" sheetId="1" r:id="R93a8d41c06dd497c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段" sheetId="2" r:id="Rb1a586a4b4584478"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类" sheetId="1" r:id="Rde018834b8ea4bdf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段" sheetId="2" r:id="R33e6fc7dedbc4403"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3488,6 +3488,31 @@
       </x:c>
       <x:c r="I70" s="26" t="str"/>
     </x:row>
+    <x:row r="71">
+      <x:c r="A71" t="str">
+        <x:v>IT</x:v>
+      </x:c>
+      <x:c r="B71" t="str">
+        <x:v>sn</x:v>
+      </x:c>
+      <x:c r="C71" t="str">
+        <x:v>序列号</x:v>
+      </x:c>
+      <x:c r="D71" t="str">
+        <x:v>单行文本</x:v>
+      </x:c>
+      <x:c r="E71"/>
+      <x:c r="F71"/>
+      <x:c r="G71" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H71" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I71" t="str">
+        <x:v>所有 IT 子分类继承，选填</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
